--- a/游戏设计王/老虎机数学专题-Megaways数学.xlsx
+++ b/游戏设计王/老虎机数学专题-Megaways数学.xlsx
@@ -3,14 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slotRtp\游戏设计王\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="Megaways 滚轮→Way计算→RTP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="122">
   <si>
     <t>Megaways Slots - 数学篇（原文数据版）</t>
   </si>
@@ -406,7 +411,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,13 +494,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -963,28 +961,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -993,122 +994,119 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1138,30 +1136,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1277,8 +1251,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6601460" y="5432425"/>
-          <a:ext cx="4729480" cy="3092450"/>
+          <a:off x="7200900" y="5419725"/>
+          <a:ext cx="5156835" cy="3079750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1315,8 +1289,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6601460" y="8626475"/>
-          <a:ext cx="4729480" cy="1959610"/>
+          <a:off x="7200900" y="8601075"/>
+          <a:ext cx="5156835" cy="1953260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1353,8 +1327,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6601460" y="10944225"/>
-          <a:ext cx="4729480" cy="2498725"/>
+          <a:off x="7200900" y="10906125"/>
+          <a:ext cx="5156835" cy="2486025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1689,11 +1663,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="94.4272727272727" customWidth="1"/>
+    <col min="1" max="1" width="94.425" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="24" width="7.85454545454545" customWidth="1"/>
+    <col min="3" max="24" width="7.85833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:10">
@@ -2215,1777 +2189,1777 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:10">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="28" t="s">
+      <c r="B18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="28" t="s">
+      <c r="A19" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1" spans="1:10">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="28" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="28" t="s">
+      <c r="B21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="28" t="s">
+      <c r="B22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="28" t="s">
+      <c r="B23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="28" t="s">
+      <c r="A24" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="33" customHeight="1" spans="1:10">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="28" t="s">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="28" t="s">
+      <c r="B26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="28" t="s">
+      <c r="B27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="28" t="s">
+      <c r="A28" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="28" t="s">
+      <c r="B29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="28" t="s">
+      <c r="B30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="28" t="s">
+      <c r="B31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="28" t="s">
+      <c r="A32" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1" spans="1:10">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="28" t="s">
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="28" t="s">
+      <c r="B34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="28" t="s">
+      <c r="B35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="28" t="s">
+      <c r="B36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="28" t="s">
+      <c r="B37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="28" t="s">
+      <c r="B38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="28" t="s">
+      <c r="B39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="28" t="s">
+      <c r="B40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="28" t="s">
+      <c r="B41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="28" t="s">
+      <c r="B42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="28" t="s">
+      <c r="B43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="28" t="s">
+      <c r="A44" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="28" t="s">
+      <c r="B45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="28" t="s">
+      <c r="B46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="28" t="s">
+      <c r="B47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="28" t="s">
+      <c r="A48" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="33" customHeight="1" spans="1:15">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="28" t="s">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="28" t="s">
+      <c r="B50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="28" t="s">
+      <c r="B51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="28" t="s">
+      <c r="B52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="28" t="s">
+      <c r="B53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:15">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="28" t="s">
+      <c r="C54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B55" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A56" s="35" t="s">
+      <c r="A56" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="36" t="s">
+      <c r="B56" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
-      <c r="N56" s="36"/>
-      <c r="O56" s="36"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="28" t="s">
+      <c r="A57" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="20.25" customHeight="1" spans="1:15">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="28" t="s">
+      <c r="B58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="28" t="s">
+      <c r="A59" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A60" s="32" t="s">
+      <c r="A60" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="28" t="s">
+      <c r="B60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A61" s="32" t="s">
+      <c r="A61" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="28" t="s">
+      <c r="B61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="33" customHeight="1" spans="1:15">
-      <c r="A62" s="32" t="s">
+      <c r="A62" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="28" t="s">
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="28" t="s">
+      <c r="B63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:15">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="28" t="s">
+      <c r="B64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="33" customHeight="1" spans="1:10">
-      <c r="A65" s="32" t="s">
+      <c r="A65" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="28" t="s">
+      <c r="B65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="33" customHeight="1" spans="1:10">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="28" t="s">
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="33" customHeight="1" spans="1:10">
-      <c r="A67" s="32" t="s">
+      <c r="A67" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="32"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="28" t="s">
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" ht="20.25" customHeight="1" spans="1:10">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="28" t="s">
+      <c r="B68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="28" t="s">
+      <c r="A69" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" spans="1:10">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B70" s="34" t="s">
+      <c r="B70" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="28" t="s">
+      <c r="C70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A71" s="35" t="s">
+      <c r="A71" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="36" t="s">
+      <c r="B71" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="28" t="s">
+      <c r="C71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A72" s="35" t="s">
+      <c r="A72" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="36" t="s">
+      <c r="B72" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="28" t="s">
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="36" t="s">
+      <c r="B73" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="36"/>
-      <c r="D73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="28" t="s">
+      <c r="C73" s="26"/>
+      <c r="D73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="36" t="s">
+      <c r="B74" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="36"/>
-      <c r="D74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="28" t="s">
+      <c r="C74" s="26"/>
+      <c r="D74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B75" s="36" t="s">
+      <c r="B75" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C75" s="36"/>
-      <c r="D75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="28" t="s">
+      <c r="C75" s="26"/>
+      <c r="D75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4021,15 +3995,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:H85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="9.28181818181818" customWidth="1"/>
-    <col min="3" max="24" width="13.5727272727273" customWidth="1"/>
+    <col min="2" max="2" width="9.28333333333333" customWidth="1"/>
+    <col min="3" max="24" width="13.575" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="15" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -4529,7 +4503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:8">
+    <row r="21" ht="15" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -4597,7 +4571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="16.5" spans="1:8">
+    <row r="24" ht="15" spans="1:8">
       <c r="A24" s="4" t="s">
         <v>85</v>
       </c>
@@ -4757,33 +4731,36 @@
       <c r="A30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3">
+        <v>2</v>
+      </c>
       <c r="C30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="3">
-        <v>6</v>
-      </c>
-      <c r="H30" s="3">
         <v>7</v>
       </c>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="3"/>
+      <c r="B31" s="6">
+        <f t="shared" ref="B31:G31" si="0">1/6</f>
+        <v>0.166666666666667</v>
+      </c>
       <c r="C31" s="6">
-        <f t="shared" ref="C31:H31" si="0">1/6</f>
+        <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
       <c r="D31" s="6">
@@ -4802,10 +4779,7 @@
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
-      <c r="H31" s="6">
-        <f t="shared" si="0"/>
-        <v>0.166666666666667</v>
-      </c>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
@@ -4813,7 +4787,7 @@
       </c>
       <c r="B32" s="7">
         <f>SUMPRODUCT(B30:G30,B31:G31)</f>
-        <v>3.33333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -4864,25 +4838,22 @@
       <c r="A34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>1</v>
+      <c r="B34" s="3">
+        <v>2</v>
       </c>
       <c r="C34" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" s="3">
-        <v>6</v>
-      </c>
-      <c r="H34" s="3">
         <v>7</v>
       </c>
     </row>
@@ -4890,30 +4861,27 @@
       <c r="A35" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>1</v>
+      <c r="B35" s="3">
+        <f t="shared" ref="B35:G35" si="1">5*B34</f>
+        <v>10</v>
       </c>
       <c r="C35" s="3">
-        <f t="shared" ref="C35:H35" si="1">5*C34</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E35" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="H35" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
@@ -4922,9 +4890,11 @@
       <c r="A36" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="3"/>
+      <c r="B36" s="5">
+        <v>5</v>
+      </c>
       <c r="C36" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D36" s="5">
         <v>0</v>
@@ -4936,9 +4906,6 @@
         <v>0</v>
       </c>
       <c r="G36" s="5">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4994,27 +4961,27 @@
       </c>
       <c r="B39" s="8">
         <f t="shared" ref="B39:G39" si="2">B26*$B$32</f>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="C39" s="8">
         <f t="shared" si="2"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="D39" s="8">
         <f t="shared" si="2"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="2"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="F39" s="8">
         <f t="shared" si="2"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="2"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>1</v>
@@ -5026,27 +4993,27 @@
       </c>
       <c r="B40" s="9">
         <f t="shared" ref="B40:G40" si="3">B26*$B$32</f>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="C40" s="9">
         <f t="shared" si="3"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="D40" s="9">
         <f t="shared" si="3"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="E40" s="9">
         <f t="shared" si="3"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="F40" s="9">
         <f t="shared" si="3"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="G40" s="9">
         <f t="shared" si="3"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>1</v>
@@ -5058,27 +5025,27 @@
       </c>
       <c r="B41" s="9">
         <f t="shared" ref="B41:G41" si="4">B26*$B$32</f>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="C41" s="9">
         <f t="shared" si="4"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="D41" s="9">
         <f t="shared" si="4"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="E41" s="9">
         <f t="shared" si="4"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="F41" s="9">
         <f t="shared" si="4"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="4"/>
-        <v>16.6666666666667</v>
+        <v>22.5</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>1</v>
@@ -5167,28 +5134,28 @@
         <v>101</v>
       </c>
       <c r="B45" s="8">
-        <f t="shared" ref="B45:G45" si="6">B36</f>
-        <v>0</v>
+        <f>B26*B31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="C45" s="8">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f>C26*C31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="D45" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D26*D31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="E45" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>E26*E31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="F45" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>F26*F31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="G45" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>G26*G31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>1</v>
@@ -5198,29 +5165,29 @@
       <c r="A46" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="9">
-        <f t="shared" ref="B46:G46" si="7">B36</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="9">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="D46" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
+      <c r="B46" s="8">
+        <f>B27*B31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="C46" s="8">
+        <f>C27*C31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D46" s="8">
+        <f>D27*D31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E46" s="8">
+        <f>E27*E31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F46" s="8">
+        <f>F27*F31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G46" s="8">
+        <f>G27*G31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>1</v>
@@ -5230,29 +5197,29 @@
       <c r="A47" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="9">
-        <f t="shared" ref="B47:G47" si="8">B36</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="9">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="D47" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
+      <c r="B47" s="8">
+        <f>B28*B31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="C47" s="8">
+        <f>C28*C31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D47" s="8">
+        <f>D28*D31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E47" s="8">
+        <f>E28*E31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F47" s="8">
+        <f>F28*F31*1</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G47" s="8">
+        <f>G28*G31*1</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>1</v>
@@ -5630,20 +5597,20 @@
         <v>6</v>
       </c>
       <c r="C63" s="9">
-        <f>B77*C77*D77*E77*F77*G77</f>
-        <v>0</v>
+        <f>B39*C39*D39*E39*F39*G39</f>
+        <v>129746337.890625</v>
       </c>
       <c r="D63" s="9">
-        <f t="shared" ref="D63:D74" si="9">C63/POWER(15,6)</f>
-        <v>0</v>
+        <f t="shared" ref="D63:D74" si="6">C63/POWER(15,6)</f>
+        <v>11.390625</v>
       </c>
       <c r="E63" s="5">
         <f>INDEX(B53:E53,4)</f>
         <v>300</v>
       </c>
       <c r="F63" s="10">
-        <f t="shared" ref="F63:F74" si="10">D63*E63/$B$57</f>
-        <v>0</v>
+        <f t="shared" ref="F63:F74" si="7">D63*E63/$B$57</f>
+        <v>3.4171875</v>
       </c>
       <c r="G63" s="6">
         <v>0.034172</v>
@@ -5661,19 +5628,19 @@
       </c>
       <c r="C64" s="9">
         <f>B77*C77*D77*E77*F77*B83</f>
-        <v>0</v>
+        <v>4805419.921875</v>
       </c>
       <c r="D64" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.421875</v>
       </c>
       <c r="E64" s="5">
         <f>INDEX(B53:E53,3)</f>
         <v>60</v>
       </c>
       <c r="F64" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0253125</v>
       </c>
       <c r="G64" s="6">
         <v>0.004219</v>
@@ -5691,19 +5658,19 @@
       </c>
       <c r="C65" s="9">
         <f>B77*C77*D77*E77*B83*B80</f>
-        <v>0</v>
+        <v>3203613.28125</v>
       </c>
       <c r="D65" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.28125</v>
       </c>
       <c r="E65" s="5">
         <f>INDEX(B53:E53,2)</f>
         <v>30</v>
       </c>
       <c r="F65" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0084375</v>
       </c>
       <c r="G65" s="6">
         <v>0.008438</v>
@@ -5721,19 +5688,19 @@
       </c>
       <c r="C66" s="9">
         <f>B77*C77*D77*B83*B80*C80</f>
-        <v>0</v>
+        <v>2135742.1875</v>
       </c>
       <c r="D66" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.1875</v>
       </c>
       <c r="E66" s="5">
         <f>INDEX(B53:E53,1)</f>
         <v>5</v>
       </c>
       <c r="F66" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0009375</v>
       </c>
       <c r="G66" s="6">
         <v>0.000938</v>
@@ -5751,19 +5718,19 @@
       </c>
       <c r="C67" s="9">
         <f>B78*C78*D78*E78*F78*G78</f>
-        <v>0</v>
+        <v>129746337.890625</v>
       </c>
       <c r="D67" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>11.390625</v>
       </c>
       <c r="E67" s="5">
         <f>INDEX(B54:E54,4)</f>
         <v>250</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>2.84765625</v>
       </c>
       <c r="G67" s="6">
         <v>0.028477</v>
@@ -5781,19 +5748,19 @@
       </c>
       <c r="C68" s="9">
         <f>B78*C78*D78*E78*F78*B84</f>
-        <v>0</v>
+        <v>4805419.921875</v>
       </c>
       <c r="D68" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.421875</v>
       </c>
       <c r="E68" s="5">
         <f>INDEX(B54:E54,3)</f>
         <v>60</v>
       </c>
       <c r="F68" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0253125</v>
       </c>
       <c r="G68" s="6">
         <v>0.004219</v>
@@ -5811,19 +5778,19 @@
       </c>
       <c r="C69" s="9">
         <f>B78*C78*D78*E78*B84*B80</f>
-        <v>0</v>
+        <v>3203613.28125</v>
       </c>
       <c r="D69" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.28125</v>
       </c>
       <c r="E69" s="5">
         <f>INDEX(B54:E54,2)</f>
         <v>30</v>
       </c>
       <c r="F69" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0084375</v>
       </c>
       <c r="G69" s="6">
         <v>0.008438</v>
@@ -5841,19 +5808,19 @@
       </c>
       <c r="C70" s="9">
         <f>B78*C78*D78*B84*B80*C80</f>
-        <v>0</v>
+        <v>2135742.1875</v>
       </c>
       <c r="D70" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.1875</v>
       </c>
       <c r="E70" s="5">
         <f>INDEX(B54:E54,1)</f>
         <v>5</v>
       </c>
       <c r="F70" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0009375</v>
       </c>
       <c r="G70" s="6">
         <v>0.000938</v>
@@ -5871,19 +5838,19 @@
       </c>
       <c r="C71" s="9">
         <f>B79*C79*D79*E79*F79*G79</f>
-        <v>0</v>
+        <v>129746337.890625</v>
       </c>
       <c r="D71" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>11.390625</v>
       </c>
       <c r="E71" s="5">
         <f>INDEX(B55:E55,4)</f>
         <v>200</v>
       </c>
       <c r="F71" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>2.278125</v>
       </c>
       <c r="G71" s="6">
         <v>0.022781</v>
@@ -5901,19 +5868,19 @@
       </c>
       <c r="C72" s="9">
         <f>B79*C79*D79*E79*F79*B85</f>
-        <v>0</v>
+        <v>4805419.921875</v>
       </c>
       <c r="D72" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.421875</v>
       </c>
       <c r="E72" s="5">
         <f>INDEX(B55:E55,3)</f>
         <v>40</v>
       </c>
       <c r="F72" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.016875</v>
       </c>
       <c r="G72" s="6">
         <v>0.001688</v>
@@ -5931,19 +5898,19 @@
       </c>
       <c r="C73" s="9">
         <f>B79*C79*D79*E79*B85*B80</f>
-        <v>0</v>
+        <v>3203613.28125</v>
       </c>
       <c r="D73" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.28125</v>
       </c>
       <c r="E73" s="5">
         <f>INDEX(B55:E55,2)</f>
         <v>20</v>
       </c>
       <c r="F73" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.005625</v>
       </c>
       <c r="G73" s="6">
         <v>0.005625</v>
@@ -5961,19 +5928,19 @@
       </c>
       <c r="C74" s="9">
         <f>B79*C79*D79*B85*B80*C80</f>
-        <v>0</v>
+        <v>2135742.1875</v>
       </c>
       <c r="D74" s="9">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.1875</v>
       </c>
       <c r="E74" s="5">
         <f>INDEX(B55:E55,1)</f>
         <v>5</v>
       </c>
       <c r="F74" s="10">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>0.0009375</v>
       </c>
       <c r="G74" s="6">
         <v>0.000938</v>
@@ -6000,7 +5967,7 @@
       </c>
       <c r="F75" s="12">
         <f>SUM(F63:F74)</f>
-        <v>0</v>
+        <v>8.63578125</v>
       </c>
       <c r="G75" s="6">
         <v>0.86302</v>
@@ -6023,13 +5990,210 @@
         <v>1</v>
       </c>
     </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77">
+        <v>22.5</v>
+      </c>
+      <c r="C77">
+        <v>22.5</v>
+      </c>
+      <c r="D77">
+        <v>22.5</v>
+      </c>
+      <c r="E77">
+        <v>22.5</v>
+      </c>
+      <c r="F77">
+        <v>22.5</v>
+      </c>
+      <c r="G77">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78">
+        <v>22.5</v>
+      </c>
+      <c r="C78">
+        <v>22.5</v>
+      </c>
+      <c r="D78">
+        <v>22.5</v>
+      </c>
+      <c r="E78">
+        <v>22.5</v>
+      </c>
+      <c r="F78">
+        <v>22.5</v>
+      </c>
+      <c r="G78">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79">
+        <v>22.5</v>
+      </c>
+      <c r="C79">
+        <v>22.5</v>
+      </c>
+      <c r="D79">
+        <v>22.5</v>
+      </c>
+      <c r="E79">
+        <v>22.5</v>
+      </c>
+      <c r="F79">
+        <v>22.5</v>
+      </c>
+      <c r="G79">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80">
+        <v>15</v>
+      </c>
+      <c r="C80">
+        <v>15</v>
+      </c>
+      <c r="D80">
+        <v>15</v>
+      </c>
+      <c r="E80">
+        <v>15</v>
+      </c>
+      <c r="F80">
+        <v>15</v>
+      </c>
+      <c r="G80">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>1</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>100</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="C83">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D83">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E83">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F83">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G83">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="C84">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D84">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E84">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F84">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G84">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="C85">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D85">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E85">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F85">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G85">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A49:C49"/>
@@ -6042,7 +6206,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M96" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A64:M76 H77:M85 A86:M96 A1:M29 A30:A31 I30:M31 A32:M33 A34:A36 I34:M36 A37:M44 A45:A47 H45:M47 A48:M62 A63:B63 D63:M63" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/游戏设计王/老虎机数学专题-Megaways数学.xlsx
+++ b/游戏设计王/老虎机数学专题-Megaways数学.xlsx
@@ -405,11 +405,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1106,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1160,6 +1161,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4755,27 +4759,27 @@
       <c r="A31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="27">
         <f t="shared" ref="B31:G31" si="0">1/6</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="27">
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="27">
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="27">
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="27">
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="27">
         <f t="shared" si="0"/>
         <v>0.166666666666667</v>
       </c>
@@ -5608,7 +5612,7 @@
         <f>INDEX(B53:E53,4)</f>
         <v>300</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63" s="28">
         <f t="shared" ref="F63:F74" si="7">D63*E63/$B$57</f>
         <v>3.4171875</v>
       </c>
@@ -5638,7 +5642,7 @@
         <f>INDEX(B53:E53,3)</f>
         <v>60</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64" s="28">
         <f t="shared" si="7"/>
         <v>0.0253125</v>
       </c>
@@ -5668,7 +5672,7 @@
         <f>INDEX(B53:E53,2)</f>
         <v>30</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65" s="28">
         <f t="shared" si="7"/>
         <v>0.0084375</v>
       </c>
@@ -5698,7 +5702,7 @@
         <f>INDEX(B53:E53,1)</f>
         <v>5</v>
       </c>
-      <c r="F66" s="10">
+      <c r="F66" s="28">
         <f t="shared" si="7"/>
         <v>0.0009375</v>
       </c>
@@ -5728,7 +5732,7 @@
         <f>INDEX(B54:E54,4)</f>
         <v>250</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F67" s="28">
         <f t="shared" si="7"/>
         <v>2.84765625</v>
       </c>
@@ -5758,7 +5762,7 @@
         <f>INDEX(B54:E54,3)</f>
         <v>60</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68" s="28">
         <f t="shared" si="7"/>
         <v>0.0253125</v>
       </c>
@@ -5788,7 +5792,7 @@
         <f>INDEX(B54:E54,2)</f>
         <v>30</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="28">
         <f t="shared" si="7"/>
         <v>0.0084375</v>
       </c>
@@ -5818,7 +5822,7 @@
         <f>INDEX(B54:E54,1)</f>
         <v>5</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="28">
         <f t="shared" si="7"/>
         <v>0.0009375</v>
       </c>
@@ -5848,7 +5852,7 @@
         <f>INDEX(B55:E55,4)</f>
         <v>200</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71" s="28">
         <f t="shared" si="7"/>
         <v>2.278125</v>
       </c>
@@ -5878,7 +5882,7 @@
         <f>INDEX(B55:E55,3)</f>
         <v>40</v>
       </c>
-      <c r="F72" s="10">
+      <c r="F72" s="28">
         <f t="shared" si="7"/>
         <v>0.016875</v>
       </c>
@@ -5908,7 +5912,7 @@
         <f>INDEX(B55:E55,2)</f>
         <v>20</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73" s="28">
         <f t="shared" si="7"/>
         <v>0.005625</v>
       </c>
@@ -5938,7 +5942,7 @@
         <f>INDEX(B55:E55,1)</f>
         <v>5</v>
       </c>
-      <c r="F74" s="10">
+      <c r="F74" s="28">
         <f t="shared" si="7"/>
         <v>0.0009375</v>
       </c>
@@ -5965,7 +5969,7 @@
       <c r="E75" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="29">
         <f>SUM(F63:F74)</f>
         <v>8.63578125</v>
       </c>
